--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -793,6 +793,103 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128862490</v>
+      </c>
+      <c r="B3" t="n">
+        <v>90526</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>522460</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7036289</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862490</v>
       </c>
       <c r="B3" t="n">
-        <v>90526</v>
+        <v>90531</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862490</v>
       </c>
       <c r="B3" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862490</v>
       </c>
       <c r="B3" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862490</v>
       </c>
       <c r="B3" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862490</v>
       </c>
       <c r="B3" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862490</v>
       </c>
       <c r="B3" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862490</v>
       </c>
       <c r="B3" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -799,7 +799,7 @@
         <v>128862490</v>
       </c>
       <c r="B3" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89046620</v>
+        <v>89046625</v>
       </c>
       <c r="B2" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99024</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,16 +686,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222771</v>
+        <v>504</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Guckusko</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cypripedium calceolus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>522276.9629692066</v>
+        <v>522371</v>
       </c>
       <c r="R2" t="n">
-        <v>7036328.123590255</v>
+        <v>7036285</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre granskog i örtrik svacka</t>
+          <t>kalkpåverkad örtrik granskog i svacka</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -796,45 +781,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128862490</v>
+        <v>89046624</v>
       </c>
       <c r="B3" t="n">
-        <v>90575</v>
+        <v>97518</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1962</v>
+        <v>1455</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Mikroskapania</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Scapania carinthiaca</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>J.B.Jack ex Lindb.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Ruven, Jmt</t>
+          <t>Skårelflyn, V om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522460</v>
+        <v>522475</v>
       </c>
       <c r="R3" t="n">
-        <v>7036289</v>
+        <v>7036260</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -861,12 +846,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -878,18 +863,238 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>i lok med dyig botten omgiven av gammal granskog</t>
+        </is>
+      </c>
+      <c r="AN3" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>3 substratenheter # tidvis dränkta, grova gamla tallågor med svart ytved</t>
+        </is>
+      </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>128862490</v>
+      </c>
+      <c r="B4" t="n">
+        <v>90932</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1962</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Vaddporing</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Anomoporia kamtschatica</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>522460</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7036289</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY3" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>89046620</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Skårelflyn, V om, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>522277</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7036328</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2020-09-15</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>äldre granskog i örtrik svacka</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27622-2025 artfynd.xlsx
+++ b/artfynd/A 27622-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046625</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046624</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -989,6 +1004,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862490</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1095,8 +1115,19 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046620</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>